--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_3_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_3_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ED760F-80D1-438A-ACFB-C024D4143BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D894BC-BF97-47D4-84C3-518612229F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,31 +55,34 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT TATACOMM 24 Apr 2025 1600 CE</t>
-  </si>
-  <si>
-    <t>23-04-2025</t>
-  </si>
-  <si>
-    <t>OPT DIVISLAB 29 May 2025 6200 CE</t>
-  </si>
-  <si>
-    <t>24-04-2025</t>
-  </si>
-  <si>
-    <t>OPT TATAELXSI 29 May 2025 5900 CE</t>
-  </si>
-  <si>
-    <t>OPT NIFTY 24 Apr 2025 24200 PE</t>
-  </si>
-  <si>
-    <t>OPT JIOFIN 29 May 2025 260 CE</t>
-  </si>
-  <si>
-    <t>25-04-2025</t>
-  </si>
-  <si>
-    <t>OPT ADANIGREEN 29 May 2025 920 PE</t>
+    <t>OPT DALBHARAT 29 May 2025 2100 PE</t>
+  </si>
+  <si>
+    <t>26-05-2025</t>
+  </si>
+  <si>
+    <t>OPT ADANIENSOL 29 May 2025 880 CE</t>
+  </si>
+  <si>
+    <t>OPT IRFC 29 May 2025 140 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 29 May 2025 24800 PE</t>
+  </si>
+  <si>
+    <t>27-05-2025</t>
+  </si>
+  <si>
+    <t>OPT HAL 29 May 2025 5000 CE</t>
+  </si>
+  <si>
+    <t>OPT TATACONSUM 29 May 2025 1130 PE</t>
+  </si>
+  <si>
+    <t>OPT BSE 26 Jun 2025 2600 CE</t>
+  </si>
+  <si>
+    <t>30-05-2025</t>
   </si>
   <si>
     <t>Buy Qty</t>
@@ -432,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
   </cols>
@@ -451,10 +454,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -463,10 +466,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -489,284 +492,331 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>257</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45770</v>
+        <v>45803</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="E2">
-        <v>27.65</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>6912.5</v>
+        <v>13475</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I2">
-        <v>19.600000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="J2">
-        <v>4900</v>
+        <v>11797.5</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-2012.5</v>
+        <v>-1677.5</v>
       </c>
       <c r="M2">
-        <v>57.17</v>
+        <v>70.03</v>
       </c>
       <c r="N2">
-        <v>-2069.67</v>
+        <v>-1747.53</v>
       </c>
       <c r="O2">
-        <v>2012.5</v>
+        <v>1677.5</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45771</v>
+        <v>45803</v>
       </c>
       <c r="D3">
-        <v>200</v>
+        <v>625</v>
       </c>
       <c r="E3">
-        <v>301.7</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>60340</v>
+        <v>11875</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>200</v>
+        <v>625</v>
       </c>
       <c r="I3">
-        <v>303.23</v>
+        <v>19.8</v>
       </c>
       <c r="J3">
-        <v>60645</v>
+        <v>12375</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>305</v>
+        <v>500</v>
       </c>
       <c r="M3">
-        <v>206.83</v>
+        <v>70.38</v>
       </c>
       <c r="N3">
-        <v>98.17</v>
+        <v>429.62</v>
       </c>
       <c r="O3">
-        <v>305</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>264</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>45771</v>
+        <v>45803</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>3525</v>
       </c>
       <c r="E4">
-        <v>203.7</v>
+        <v>2.4</v>
       </c>
       <c r="F4">
-        <v>20370</v>
+        <v>8460</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>3525</v>
       </c>
       <c r="I4">
-        <v>206.7</v>
+        <v>2.15</v>
       </c>
       <c r="J4">
-        <v>20670</v>
+        <v>7578.75</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>300</v>
+        <v>-881.25</v>
       </c>
       <c r="M4">
-        <v>85.73</v>
+        <v>61.77</v>
       </c>
       <c r="N4">
-        <v>214.27</v>
+        <v>-943.02</v>
       </c>
       <c r="O4">
-        <v>300</v>
+        <v>881.25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>45771</v>
+        <v>45804</v>
       </c>
       <c r="D5">
         <v>75</v>
       </c>
       <c r="E5">
-        <v>3.7</v>
+        <v>212.55</v>
       </c>
       <c r="F5">
-        <v>277.5</v>
+        <v>15941.25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5">
         <v>75</v>
       </c>
       <c r="I5">
-        <v>1.8</v>
+        <v>220.6</v>
       </c>
       <c r="J5">
-        <v>135</v>
+        <v>16545</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>-142.5</v>
+        <v>603.75</v>
       </c>
       <c r="M5">
-        <v>47.52</v>
+        <v>77.89</v>
       </c>
       <c r="N5">
-        <v>-190.02</v>
+        <v>525.86</v>
       </c>
       <c r="O5">
-        <v>142.5</v>
+        <v>603.75</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45772</v>
+        <v>45804</v>
       </c>
       <c r="D6">
-        <v>3300</v>
+        <v>150</v>
       </c>
       <c r="E6">
-        <v>11.18</v>
+        <v>116.35</v>
       </c>
       <c r="F6">
-        <v>36877.5</v>
+        <v>17452.5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>3300</v>
+        <v>150</v>
       </c>
       <c r="I6">
-        <v>10.15</v>
+        <v>120.25</v>
       </c>
       <c r="J6">
-        <v>33495</v>
+        <v>18037.5</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-3382.5</v>
+        <v>585</v>
       </c>
       <c r="M6">
-        <v>135</v>
+        <v>80.959999999999994</v>
       </c>
       <c r="N6">
-        <v>-3517.5</v>
+        <v>504.04</v>
       </c>
       <c r="O6">
-        <v>3382.5</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>258</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45804</v>
+      </c>
+      <c r="D7">
+        <v>456</v>
+      </c>
+      <c r="E7">
+        <v>13.05</v>
+      </c>
+      <c r="F7">
+        <v>5950.8</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>456</v>
+      </c>
+      <c r="I7">
+        <v>13.05</v>
+      </c>
+      <c r="J7">
+        <v>5950.8</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>58.33</v>
+      </c>
+      <c r="N7">
+        <v>-58.33</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1">
-        <v>45772</v>
-      </c>
-      <c r="D7">
-        <v>375</v>
-      </c>
-      <c r="E7">
-        <v>63.65</v>
-      </c>
-      <c r="F7">
-        <v>23868.75</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>375</v>
-      </c>
-      <c r="I7">
-        <v>60.05</v>
-      </c>
-      <c r="J7">
-        <v>22518.75</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>-1350</v>
-      </c>
-      <c r="M7">
-        <v>90.09</v>
-      </c>
-      <c r="N7">
-        <v>-1440.09</v>
-      </c>
-      <c r="O7">
-        <v>1350</v>
+      <c r="C8" s="1">
+        <v>45807</v>
+      </c>
+      <c r="D8">
+        <v>750</v>
+      </c>
+      <c r="E8">
+        <v>148</v>
+      </c>
+      <c r="F8">
+        <v>111000</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>750</v>
+      </c>
+      <c r="I8">
+        <v>147.15</v>
+      </c>
+      <c r="J8">
+        <v>110362.5</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>-637.5</v>
+      </c>
+      <c r="M8">
+        <v>300.47000000000003</v>
+      </c>
+      <c r="N8">
+        <v>-937.97</v>
+      </c>
+      <c r="O8">
+        <v>637.5</v>
       </c>
     </row>
   </sheetData>
